--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.134.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.134.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.134.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.134.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN :: æ²™</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+6C99 CJK UNIFIED IDEOGRAPH-6C99 | isolated marker/symbol line :: 沙</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: ï»¿ORDERS OF JANUARY 1851,â€˜â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851,‘‘</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851,‘‘</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L22: isolated marker/symbol line :: 4</t>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,19 +676,19 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L129: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: relief ; pray subpenaÃ¦na, &amp;c.)</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: ， c.</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”If the plaintiff is the executor or administrator, or Alterations</t>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 127</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+6C99 CJK UNIFIED IDEOGRAPH-6C99 | isolated marker/symbol line :: 沙</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -735,19 +739,19 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L141: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L45: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: ，&amp; c.</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”â€”,but now deceased, who departed this life on or</t>
+          <t>L127: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 5.</t>
+          <t>L35: isolated marker/symbol line :: 127</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -782,12 +786,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -796,17 +800,17 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”, and</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>L116: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: 2 ， 8. C.</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: d</t>
+          <t>L103: isolated marker/symbol line :: 5.</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -847,22 +851,22 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>L141: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: 5</t>
+          <t>L112: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -899,21 +903,17 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L141: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L113: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L127: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -955,7 +955,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L142: symbol-only separator/garbage line :: . 6.</t>
+          <t>L141: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -996,7 +996,11 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L142: symbol-only separator/garbage line :: . 6.</t>
+        </is>
+      </c>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
@@ -1017,12 +1021,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1061,7 +1065,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1095,7 +1099,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
